--- a/data/2FEB_25_26/players_25_26_2FEB.xlsx
+++ b/data/2FEB_25_26/players_25_26_2FEB.xlsx
@@ -557,22 +557,22 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>48.13333333333333</v>
+        <v>64</v>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
         <v>5</v>
@@ -581,25 +581,25 @@
         <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
         <v>7</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
         <v>5</v>
       </c>
       <c r="N2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="W2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -650,22 +650,22 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>406.0333333333334</v>
+        <v>430.3</v>
       </c>
       <c r="B3" t="n">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="C3" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D3" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F3" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G3" t="n">
         <v>33</v>
@@ -674,13 +674,13 @@
         <v>50</v>
       </c>
       <c r="I3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J3" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L3" t="n">
         <v>13</v>
@@ -689,13 +689,13 @@
         <v>19</v>
       </c>
       <c r="N3" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="O3" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="W3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -743,49 +743,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>405.1333333333333</v>
+        <v>418.8833333333333</v>
       </c>
       <c r="B4" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="C4" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E4" t="n">
         <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H4" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K4" t="n">
         <v>12</v>
       </c>
       <c r="L4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O4" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P4" t="n">
         <v>4</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="W4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>245.35</v>
+        <v>258.4666666666667</v>
       </c>
       <c r="B5" t="n">
         <v>44</v>
@@ -851,7 +851,7 @@
         <v>8</v>
       </c>
       <c r="F5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G5" t="n">
         <v>2</v>
@@ -860,25 +860,25 @@
         <v>7</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J5" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M5" t="n">
         <v>12</v>
       </c>
       <c r="N5" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="W5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1115,22 +1115,22 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>51.83333333333334</v>
+        <v>55.35</v>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -1139,7 +1139,7 @@
         <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
         <v>3</v>
@@ -1148,7 +1148,7 @@
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
         <v>1</v>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="W8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1301,49 +1301,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>483.2166666666667</v>
+        <v>500.15</v>
       </c>
       <c r="B10" t="n">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C10" t="n">
         <v>55</v>
       </c>
       <c r="D10" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E10" t="n">
         <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G10" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H10" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J10" t="n">
         <v>43</v>
       </c>
       <c r="K10" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="L10" t="n">
         <v>23</v>
       </c>
       <c r="M10" t="n">
+        <v>43</v>
+      </c>
+      <c r="N10" t="n">
         <v>41</v>
       </c>
-      <c r="N10" t="n">
-        <v>40</v>
-      </c>
       <c r="O10" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="W10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1394,22 +1394,22 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>484.2333333333333</v>
+        <v>507.7833333333334</v>
       </c>
       <c r="B11" t="n">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="C11" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D11" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E11" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F11" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G11" t="n">
         <v>51</v>
@@ -1418,7 +1418,7 @@
         <v>65</v>
       </c>
       <c r="I11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J11" t="n">
         <v>31</v>
@@ -1427,13 +1427,13 @@
         <v>10</v>
       </c>
       <c r="L11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M11" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N11" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O11" t="n">
         <v>50</v>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="W11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -1487,22 +1487,22 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>549.0333333333333</v>
+        <v>562.9833333333333</v>
       </c>
       <c r="B12" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C12" t="n">
         <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="E12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F12" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G12" t="n">
         <v>44</v>
@@ -1511,7 +1511,7 @@
         <v>58</v>
       </c>
       <c r="I12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J12" t="n">
         <v>43</v>
@@ -1526,7 +1526,7 @@
         <v>29</v>
       </c>
       <c r="N12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O12" t="n">
         <v>48</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="W12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -1580,16 +1580,16 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>324.55</v>
+        <v>342.2333333333333</v>
       </c>
       <c r="B13" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C13" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E13" t="n">
         <v>2</v>
@@ -1604,13 +1604,13 @@
         <v>26</v>
       </c>
       <c r="I13" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J13" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L13" t="n">
         <v>5</v>
@@ -1619,10 +1619,10 @@
         <v>22</v>
       </c>
       <c r="N13" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P13" t="n">
         <v>17</v>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="W13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -1673,22 +1673,22 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>575.0666666666666</v>
+        <v>596.1</v>
       </c>
       <c r="B14" t="n">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="E14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F14" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G14" t="n">
         <v>35</v>
@@ -1697,28 +1697,28 @@
         <v>51</v>
       </c>
       <c r="I14" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J14" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K14" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M14" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="N14" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="O14" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="P14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="W14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>287.3833333333333</v>
+        <v>297.3666666666667</v>
       </c>
       <c r="B15" t="n">
         <v>90</v>
@@ -1775,13 +1775,13 @@
         <v>27</v>
       </c>
       <c r="D15" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E15" t="n">
         <v>7</v>
       </c>
       <c r="F15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G15" t="n">
         <v>15</v>
@@ -1790,25 +1790,25 @@
         <v>20</v>
       </c>
       <c r="I15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J15" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K15" t="n">
         <v>6</v>
       </c>
       <c r="L15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M15" t="n">
         <v>16</v>
       </c>
       <c r="N15" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P15" t="n">
         <v>4</v>
@@ -1844,7 +1844,7 @@
         </is>
       </c>
       <c r="W15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -1859,49 +1859,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>287.1166666666667</v>
+        <v>313.4666666666666</v>
       </c>
       <c r="B16" t="n">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G16" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I16" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="J16" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K16" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L16" t="n">
         <v>16</v>
       </c>
       <c r="M16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N16" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="O16" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="P16" t="n">
         <v>7</v>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="W16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -1952,49 +1952,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>248.8833333333333</v>
+        <v>281.6333333333333</v>
       </c>
       <c r="B17" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C17" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D17" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E17" t="n">
         <v>16</v>
       </c>
       <c r="F17" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G17" t="n">
         <v>12</v>
       </c>
       <c r="H17" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K17" t="n">
         <v>7</v>
       </c>
       <c r="L17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M17" t="n">
         <v>8</v>
       </c>
       <c r="N17" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="O17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P17" t="n">
         <v>3</v>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="W17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2045,10 +2045,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>366.2333333333333</v>
+        <v>383.5</v>
       </c>
       <c r="B18" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C18" t="n">
         <v>6</v>
@@ -2057,10 +2057,10 @@
         <v>14</v>
       </c>
       <c r="E18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F18" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G18" t="n">
         <v>4</v>
@@ -2072,10 +2072,10 @@
         <v>6</v>
       </c>
       <c r="J18" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L18" t="n">
         <v>12</v>
@@ -2084,7 +2084,7 @@
         <v>13</v>
       </c>
       <c r="N18" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="O18" t="n">
         <v>17</v>
@@ -2123,7 +2123,7 @@
         </is>
       </c>
       <c r="W18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2138,16 +2138,16 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>521.7166666666667</v>
+        <v>540.5666666666667</v>
       </c>
       <c r="B19" t="n">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C19" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D19" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E19" t="n">
         <v>22</v>
@@ -2165,22 +2165,22 @@
         <v>13</v>
       </c>
       <c r="J19" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K19" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M19" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N19" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O19" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P19" t="n">
         <v>1</v>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="W19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2603,49 +2603,49 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>391.7833333333333</v>
+        <v>421.2333333333333</v>
       </c>
       <c r="B24" t="n">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="C24" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D24" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E24" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F24" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="G24" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="H24" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I24" t="n">
         <v>5</v>
       </c>
       <c r="J24" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K24" t="n">
+        <v>49</v>
+      </c>
+      <c r="L24" t="n">
+        <v>16</v>
+      </c>
+      <c r="M24" t="n">
+        <v>31</v>
+      </c>
+      <c r="N24" t="n">
         <v>46</v>
       </c>
-      <c r="L24" t="n">
-        <v>13</v>
-      </c>
-      <c r="M24" t="n">
-        <v>29</v>
-      </c>
-      <c r="N24" t="n">
-        <v>45</v>
-      </c>
       <c r="O24" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -2681,7 +2681,7 @@
         </is>
       </c>
       <c r="W24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>502.65</v>
+        <v>512.3666666666667</v>
       </c>
       <c r="B30" t="n">
         <v>116</v>
@@ -3176,7 +3176,7 @@
         <v>22</v>
       </c>
       <c r="F30" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G30" t="n">
         <v>24</v>
@@ -3188,19 +3188,19 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K30" t="n">
         <v>12</v>
       </c>
       <c r="L30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M30" t="n">
         <v>14</v>
       </c>
       <c r="N30" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O30" t="n">
         <v>41</v>
@@ -3239,7 +3239,7 @@
         </is>
       </c>
       <c r="W30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3254,49 +3254,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>166.7333333333333</v>
+        <v>205.35</v>
       </c>
       <c r="B31" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="C31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D31" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F31" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G31" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H31" t="n">
+        <v>24</v>
+      </c>
+      <c r="I31" t="n">
+        <v>13</v>
+      </c>
+      <c r="J31" t="n">
         <v>20</v>
       </c>
-      <c r="I31" t="n">
-        <v>11</v>
-      </c>
-      <c r="J31" t="n">
-        <v>17</v>
-      </c>
       <c r="K31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L31" t="n">
         <v>6</v>
       </c>
       <c r="M31" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N31" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="O31" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="P31" t="n">
         <v>2</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="W31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3347,16 +3347,16 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>604.4833333333333</v>
+        <v>632.5333333333333</v>
       </c>
       <c r="B32" t="n">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="C32" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D32" t="n">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -3365,31 +3365,31 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H32" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="I32" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J32" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="K32" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M32" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="N32" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="O32" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="P32" t="n">
         <v>1</v>
@@ -3425,7 +3425,7 @@
         </is>
       </c>
       <c r="W32" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3440,49 +3440,49 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>508.3</v>
+        <v>543.5333333333333</v>
       </c>
       <c r="B33" t="n">
-        <v>281</v>
+        <v>306</v>
       </c>
       <c r="C33" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D33" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E33" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F33" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G33" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H33" t="n">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="I33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J33" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K33" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="L33" t="n">
         <v>25</v>
       </c>
       <c r="M33" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N33" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O33" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="P33" t="n">
         <v>2</v>
@@ -3518,7 +3518,7 @@
         </is>
       </c>
       <c r="W33" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -3533,16 +3533,16 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3.4</v>
+        <v>18.46666666666667</v>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -3551,31 +3551,31 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
         <v>1</v>
       </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="W34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -3626,22 +3626,22 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>282.95</v>
+        <v>313.6666666666666</v>
       </c>
       <c r="B35" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="C35" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D35" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E35" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F35" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G35" t="n">
         <v>6</v>
@@ -3656,13 +3656,13 @@
         <v>14</v>
       </c>
       <c r="K35" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="L35" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M35" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N35" t="n">
         <v>10</v>
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="W35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -3719,16 +3719,16 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>646.0666666666666</v>
+        <v>676.5</v>
       </c>
       <c r="B36" t="n">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C36" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D36" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E36" t="n">
         <v>14</v>
@@ -3737,31 +3737,31 @@
         <v>49</v>
       </c>
       <c r="G36" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H36" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I36" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J36" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K36" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L36" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M36" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N36" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="O36" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="P36" t="n">
         <v>1</v>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="W36" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -3905,37 +3905,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>431.3333333333333</v>
+        <v>463</v>
       </c>
       <c r="B38" t="n">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="C38" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D38" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="E38" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F38" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G38" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H38" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I38" t="n">
         <v>30</v>
       </c>
       <c r="J38" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K38" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L38" t="n">
         <v>8</v>
@@ -3944,10 +3944,10 @@
         <v>25</v>
       </c>
       <c r="N38" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="O38" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -3983,7 +3983,7 @@
         </is>
       </c>
       <c r="W38" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>37.08333333333334</v>
+        <v>42.71666666666667</v>
       </c>
       <c r="B42" t="n">
         <v>5</v>
@@ -4316,7 +4316,7 @@
         <v>5</v>
       </c>
       <c r="N42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="W42" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4556,37 +4556,37 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>464.4166666666667</v>
+        <v>479.7</v>
       </c>
       <c r="B45" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C45" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D45" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E45" t="n">
         <v>20</v>
       </c>
       <c r="F45" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G45" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H45" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I45" t="n">
         <v>10</v>
       </c>
       <c r="J45" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K45" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="L45" t="n">
         <v>24</v>
@@ -4595,10 +4595,10 @@
         <v>48</v>
       </c>
       <c r="N45" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O45" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="P45" t="n">
         <v>0</v>
@@ -4634,7 +4634,7 @@
         </is>
       </c>
       <c r="W45" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -4742,49 +4742,49 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117.0166666666667</v>
+        <v>124.1</v>
       </c>
       <c r="B47" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C47" t="n">
         <v>8</v>
       </c>
       <c r="D47" t="n">
+        <v>22</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" t="n">
+        <v>14</v>
+      </c>
+      <c r="G47" t="n">
+        <v>13</v>
+      </c>
+      <c r="H47" t="n">
         <v>21</v>
       </c>
-      <c r="E47" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" t="n">
-        <v>13</v>
-      </c>
-      <c r="G47" t="n">
-        <v>12</v>
-      </c>
-      <c r="H47" t="n">
-        <v>19</v>
-      </c>
       <c r="I47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J47" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K47" t="n">
         <v>4</v>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M47" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N47" t="n">
         <v>20</v>
       </c>
       <c r="O47" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="P47" t="n">
         <v>6</v>
@@ -4820,7 +4820,7 @@
         </is>
       </c>
       <c r="W47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -4835,49 +4835,49 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>637.15</v>
+        <v>657.6</v>
       </c>
       <c r="B48" t="n">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="C48" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D48" t="n">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="E48" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F48" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G48" t="n">
+        <v>84</v>
+      </c>
+      <c r="H48" t="n">
+        <v>111</v>
+      </c>
+      <c r="I48" t="n">
+        <v>17</v>
+      </c>
+      <c r="J48" t="n">
         <v>81</v>
-      </c>
-      <c r="H48" t="n">
-        <v>105</v>
-      </c>
-      <c r="I48" t="n">
-        <v>16</v>
-      </c>
-      <c r="J48" t="n">
-        <v>80</v>
       </c>
       <c r="K48" t="n">
         <v>14</v>
       </c>
       <c r="L48" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M48" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N48" t="n">
         <v>50</v>
       </c>
       <c r="O48" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="P48" t="n">
         <v>9</v>
@@ -4913,7 +4913,7 @@
         </is>
       </c>
       <c r="W48" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -4928,22 +4928,22 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>597.6</v>
+        <v>616.3333333333334</v>
       </c>
       <c r="B49" t="n">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="C49" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D49" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E49" t="n">
         <v>61</v>
       </c>
       <c r="F49" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="G49" t="n">
         <v>47</v>
@@ -4955,25 +4955,25 @@
         <v>9</v>
       </c>
       <c r="J49" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K49" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L49" t="n">
         <v>44</v>
       </c>
       <c r="M49" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="N49" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="O49" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="P49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="W49" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5300,22 +5300,22 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128.5166666666667</v>
+        <v>156.1166666666667</v>
       </c>
       <c r="B53" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="C53" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D53" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E53" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F53" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G53" t="n">
         <v>11</v>
@@ -5324,25 +5324,25 @@
         <v>14</v>
       </c>
       <c r="I53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J53" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K53" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L53" t="n">
         <v>2</v>
       </c>
       <c r="M53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N53" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O53" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P53" t="n">
         <v>3</v>
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="W53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5393,16 +5393,16 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>62.93333333333334</v>
+        <v>75.33333333333334</v>
       </c>
       <c r="B54" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C54" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D54" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
@@ -5417,28 +5417,28 @@
         <v>9</v>
       </c>
       <c r="I54" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N54" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O54" t="n">
         <v>9</v>
       </c>
       <c r="P54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="W54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5486,22 +5486,22 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123.1</v>
+        <v>140.0833333333333</v>
       </c>
       <c r="B55" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C55" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D55" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F55" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G55" t="n">
         <v>9</v>
@@ -5510,22 +5510,22 @@
         <v>13</v>
       </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J55" t="n">
         <v>5</v>
       </c>
       <c r="K55" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L55" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N55" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O55" t="n">
         <v>11</v>
@@ -5564,7 +5564,7 @@
         </is>
       </c>
       <c r="W55" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5672,34 +5672,34 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>327.75</v>
+        <v>345.5333333333333</v>
       </c>
       <c r="B57" t="n">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="C57" t="n">
+        <v>19</v>
+      </c>
+      <c r="D57" t="n">
+        <v>45</v>
+      </c>
+      <c r="E57" t="n">
+        <v>24</v>
+      </c>
+      <c r="F57" t="n">
+        <v>81</v>
+      </c>
+      <c r="G57" t="n">
+        <v>37</v>
+      </c>
+      <c r="H57" t="n">
+        <v>51</v>
+      </c>
+      <c r="I57" t="n">
         <v>17</v>
       </c>
-      <c r="D57" t="n">
-        <v>40</v>
-      </c>
-      <c r="E57" t="n">
-        <v>23</v>
-      </c>
-      <c r="F57" t="n">
-        <v>79</v>
-      </c>
-      <c r="G57" t="n">
-        <v>36</v>
-      </c>
-      <c r="H57" t="n">
-        <v>50</v>
-      </c>
-      <c r="I57" t="n">
-        <v>16</v>
-      </c>
       <c r="J57" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K57" t="n">
         <v>12</v>
@@ -5708,16 +5708,16 @@
         <v>7</v>
       </c>
       <c r="M57" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N57" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O57" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
         </is>
       </c>
       <c r="W57" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5765,49 +5765,49 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>468.25</v>
+        <v>493.0666666666667</v>
       </c>
       <c r="B58" t="n">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="C58" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D58" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E58" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F58" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="G58" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H58" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I58" t="n">
         <v>13</v>
       </c>
       <c r="J58" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K58" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L58" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M58" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N58" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="O58" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="P58" t="n">
         <v>1</v>
@@ -5843,7 +5843,7 @@
         </is>
       </c>
       <c r="W58" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -5858,22 +5858,22 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>489.7166666666667</v>
+        <v>500.6</v>
       </c>
       <c r="B59" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C59" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D59" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E59" t="n">
         <v>19</v>
       </c>
       <c r="F59" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G59" t="n">
         <v>32</v>
@@ -5885,10 +5885,10 @@
         <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K59" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L59" t="n">
         <v>22</v>
@@ -5897,7 +5897,7 @@
         <v>17</v>
       </c>
       <c r="N59" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="O59" t="n">
         <v>45</v>
@@ -5936,7 +5936,7 @@
         </is>
       </c>
       <c r="W59" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6044,16 +6044,16 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>593.1666666666666</v>
+        <v>611.9333333333333</v>
       </c>
       <c r="B61" t="n">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="C61" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D61" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E61" t="n">
         <v>19</v>
@@ -6062,19 +6062,19 @@
         <v>80</v>
       </c>
       <c r="G61" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H61" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="I61" t="n">
         <v>45</v>
       </c>
       <c r="J61" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K61" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L61" t="n">
         <v>16</v>
@@ -6083,13 +6083,13 @@
         <v>47</v>
       </c>
       <c r="N61" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O61" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="P61" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         </is>
       </c>
       <c r="W61" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>464.7333333333333</v>
+        <v>489.3</v>
       </c>
       <c r="B62" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C62" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D62" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E62" t="n">
         <v>28</v>
       </c>
       <c r="F62" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G62" t="n">
         <v>10</v>
@@ -6161,25 +6161,25 @@
         <v>15</v>
       </c>
       <c r="I62" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="K62" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L62" t="n">
         <v>17</v>
       </c>
       <c r="M62" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N62" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="O62" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P62" t="n">
         <v>1</v>
@@ -6215,7 +6215,7 @@
         </is>
       </c>
       <c r="W62" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6230,22 +6230,22 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>249.6833333333333</v>
+        <v>267.65</v>
       </c>
       <c r="B63" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C63" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D63" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F63" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G63" t="n">
         <v>13</v>
@@ -6254,25 +6254,25 @@
         <v>18</v>
       </c>
       <c r="I63" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J63" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K63" t="n">
         <v>14</v>
       </c>
       <c r="L63" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M63" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="N63" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O63" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P63" t="n">
         <v>5</v>
@@ -6308,7 +6308,7 @@
         </is>
       </c>
       <c r="W63" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6323,16 +6323,16 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>73.28333333333333</v>
+        <v>96.3</v>
       </c>
       <c r="B64" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D64" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -6341,32 +6341,32 @@
         <v>5</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J64" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K64" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L64" t="n">
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N64" t="n">
+        <v>11</v>
+      </c>
+      <c r="O64" t="n">
         <v>10</v>
       </c>
-      <c r="O64" t="n">
-        <v>8</v>
-      </c>
       <c r="P64" t="n">
         <v>0</v>
       </c>
@@ -6401,7 +6401,7 @@
         </is>
       </c>
       <c r="W64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6602,16 +6602,16 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>404.5666666666667</v>
+        <v>430.35</v>
       </c>
       <c r="B67" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="C67" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D67" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
@@ -6629,10 +6629,10 @@
         <v>61</v>
       </c>
       <c r="J67" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K67" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L67" t="n">
         <v>19</v>
@@ -6641,13 +6641,13 @@
         <v>38</v>
       </c>
       <c r="N67" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O67" t="n">
         <v>46</v>
       </c>
       <c r="P67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         </is>
       </c>
       <c r="W67" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6881,49 +6881,49 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>303.45</v>
+        <v>322.8833333333333</v>
       </c>
       <c r="B70" t="n">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="C70" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D70" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E70" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F70" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G70" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H70" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I70" t="n">
         <v>5</v>
       </c>
       <c r="J70" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K70" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L70" t="n">
         <v>12</v>
       </c>
       <c r="M70" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N70" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="O70" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="P70" t="n">
         <v>1</v>
@@ -6959,7 +6959,7 @@
         </is>
       </c>
       <c r="W70" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -6974,16 +6974,16 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>437.95</v>
+        <v>468.95</v>
       </c>
       <c r="B71" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C71" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D71" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E71" t="n">
         <v>3</v>
@@ -6992,31 +6992,31 @@
         <v>9</v>
       </c>
       <c r="G71" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H71" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I71" t="n">
         <v>40</v>
       </c>
       <c r="J71" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="K71" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="L71" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M71" t="n">
         <v>25</v>
       </c>
       <c r="N71" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O71" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="P71" t="n">
         <v>2</v>
@@ -7052,7 +7052,7 @@
         </is>
       </c>
       <c r="W71" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7160,16 +7160,16 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>182.3333333333333</v>
+        <v>187.5666666666667</v>
       </c>
       <c r="B73" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D73" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E73" t="n">
         <v>3</v>
@@ -7187,7 +7187,7 @@
         <v>1</v>
       </c>
       <c r="J73" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K73" t="n">
         <v>19</v>
@@ -7199,7 +7199,7 @@
         <v>18</v>
       </c>
       <c r="N73" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O73" t="n">
         <v>8</v>
@@ -7238,7 +7238,7 @@
         </is>
       </c>
       <c r="W73" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7253,22 +7253,22 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>509.5833333333333</v>
+        <v>528.9666666666667</v>
       </c>
       <c r="B74" t="n">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C74" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D74" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E74" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F74" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G74" t="n">
         <v>20</v>
@@ -7283,16 +7283,16 @@
         <v>26</v>
       </c>
       <c r="K74" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L74" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M74" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="N74" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="O74" t="n">
         <v>51</v>
@@ -7331,7 +7331,7 @@
         </is>
       </c>
       <c r="W74" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7346,28 +7346,28 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>583.3666666666667</v>
+        <v>605.3333333333334</v>
       </c>
       <c r="B75" t="n">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C75" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D75" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E75" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F75" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="G75" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H75" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I75" t="n">
         <v>15</v>
@@ -7376,19 +7376,19 @@
         <v>56</v>
       </c>
       <c r="K75" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L75" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M75" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="N75" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="O75" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="P75" t="n">
         <v>0</v>
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="W75" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7439,10 +7439,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>218.35</v>
+        <v>230.3833333333333</v>
       </c>
       <c r="B76" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C76" t="n">
         <v>4</v>
@@ -7451,10 +7451,10 @@
         <v>13</v>
       </c>
       <c r="E76" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F76" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G76" t="n">
         <v>3</v>
@@ -7469,16 +7469,16 @@
         <v>12</v>
       </c>
       <c r="K76" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L76" t="n">
         <v>11</v>
       </c>
       <c r="M76" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N76" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O76" t="n">
         <v>6</v>
@@ -7517,7 +7517,7 @@
         </is>
       </c>
       <c r="W76" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7532,10 +7532,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>480.9833333333333</v>
+        <v>494.25</v>
       </c>
       <c r="B77" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C77" t="n">
         <v>45</v>
@@ -7550,16 +7550,16 @@
         <v>15</v>
       </c>
       <c r="G77" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H77" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I77" t="n">
         <v>30</v>
       </c>
       <c r="J77" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K77" t="n">
         <v>27</v>
@@ -7568,13 +7568,13 @@
         <v>15</v>
       </c>
       <c r="M77" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N77" t="n">
         <v>47</v>
       </c>
       <c r="O77" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P77" t="n">
         <v>11</v>
@@ -7610,7 +7610,7 @@
         </is>
       </c>
       <c r="W77" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7811,34 +7811,34 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>335.1166666666667</v>
+        <v>370.2333333333333</v>
       </c>
       <c r="B80" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="C80" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D80" t="n">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="E80" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F80" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G80" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H80" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I80" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J80" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K80" t="n">
         <v>14</v>
@@ -7847,49 +7847,49 @@
         <v>14</v>
       </c>
       <c r="M80" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N80" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="O80" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="P80" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>https://imagenes.feb.es/Foto.aspx?c=2527396</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>SANTOS SPENCER, PATRICK JUNIOR</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>https://baloncestoenvivo.feb.es/Jugador.aspx?i=980009&amp;c=2527396</t>
+        </is>
+      </c>
+      <c r="W80" t="n">
         <v>16</v>
-      </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="R80" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>https://imagenes.feb.es/Foto.aspx?c=2527396</t>
-        </is>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>SANTOS SPENCER, PATRICK JUNIOR</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>https://baloncestoenvivo.feb.es/Jugador.aspx?i=980009&amp;c=2527396</t>
-        </is>
-      </c>
-      <c r="W80" t="n">
-        <v>15</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8090,49 +8090,49 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>545.4166666666666</v>
+        <v>568.1166666666667</v>
       </c>
       <c r="B83" t="n">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="C83" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D83" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E83" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F83" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G83" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H83" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="I83" t="n">
         <v>8</v>
       </c>
       <c r="J83" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K83" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L83" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M83" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N83" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="O83" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="P83" t="n">
         <v>3</v>
@@ -8168,7 +8168,7 @@
         </is>
       </c>
       <c r="W83" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8183,22 +8183,22 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>206.85</v>
+        <v>229.9833333333333</v>
       </c>
       <c r="B84" t="n">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="C84" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D84" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E84" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F84" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G84" t="n">
         <v>10</v>
@@ -8210,7 +8210,7 @@
         <v>10</v>
       </c>
       <c r="J84" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K84" t="n">
         <v>8</v>
@@ -8219,13 +8219,13 @@
         <v>13</v>
       </c>
       <c r="M84" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N84" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="O84" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P84" t="n">
         <v>0</v>
@@ -8261,7 +8261,7 @@
         </is>
       </c>
       <c r="W84" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8276,16 +8276,16 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>533.4</v>
+        <v>565.3333333333334</v>
       </c>
       <c r="B85" t="n">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="C85" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D85" t="n">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="E85" t="n">
         <v>2</v>
@@ -8294,31 +8294,31 @@
         <v>7</v>
       </c>
       <c r="G85" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H85" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="I85" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J85" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="K85" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L85" t="n">
         <v>24</v>
       </c>
       <c r="M85" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="N85" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O85" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="P85" t="n">
         <v>21</v>
@@ -8354,7 +8354,7 @@
         </is>
       </c>
       <c r="W85" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>407.1166666666667</v>
+        <v>416.35</v>
       </c>
       <c r="B86" t="n">
         <v>140</v>
@@ -8378,13 +8378,13 @@
         <v>33</v>
       </c>
       <c r="D86" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E86" t="n">
         <v>17</v>
       </c>
       <c r="F86" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G86" t="n">
         <v>23</v>
@@ -8405,13 +8405,13 @@
         <v>3</v>
       </c>
       <c r="M86" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N86" t="n">
         <v>36</v>
       </c>
       <c r="O86" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P86" t="n">
         <v>7</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="W86" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8462,7 +8462,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>324.4833333333333</v>
+        <v>345.9833333333333</v>
       </c>
       <c r="B87" t="n">
         <v>160</v>
@@ -8471,7 +8471,7 @@
         <v>33</v>
       </c>
       <c r="D87" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E87" t="n">
         <v>21</v>
@@ -8486,22 +8486,22 @@
         <v>46</v>
       </c>
       <c r="I87" t="n">
+        <v>24</v>
+      </c>
+      <c r="J87" t="n">
+        <v>51</v>
+      </c>
+      <c r="K87" t="n">
         <v>23</v>
       </c>
-      <c r="J87" t="n">
-        <v>46</v>
-      </c>
-      <c r="K87" t="n">
-        <v>22</v>
-      </c>
       <c r="L87" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M87" t="n">
         <v>15</v>
       </c>
       <c r="N87" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O87" t="n">
         <v>43</v>
@@ -8540,7 +8540,7 @@
         </is>
       </c>
       <c r="W87" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8555,49 +8555,49 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>660.8833333333333</v>
+        <v>688.65</v>
       </c>
       <c r="B88" t="n">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="C88" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D88" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E88" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F88" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G88" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H88" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I88" t="n">
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K88" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L88" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M88" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N88" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O88" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="P88" t="n">
         <v>2</v>
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="W88" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8648,49 +8648,49 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>715.4</v>
+        <v>743.2833333333333</v>
       </c>
       <c r="B89" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C89" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D89" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E89" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F89" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G89" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H89" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I89" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J89" t="n">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="K89" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="L89" t="n">
         <v>21</v>
       </c>
       <c r="M89" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="N89" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O89" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="P89" t="n">
         <v>5</v>
@@ -8726,7 +8726,7 @@
         </is>
       </c>
       <c r="W89" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8741,16 +8741,16 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>465.8166666666667</v>
+        <v>485.8166666666667</v>
       </c>
       <c r="B90" t="n">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="C90" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D90" t="n">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="E90" t="n">
         <v>3</v>
@@ -8759,34 +8759,34 @@
         <v>5</v>
       </c>
       <c r="G90" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H90" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="I90" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J90" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="K90" t="n">
         <v>9</v>
       </c>
       <c r="L90" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M90" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N90" t="n">
         <v>42</v>
       </c>
       <c r="O90" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="P90" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         </is>
       </c>
       <c r="W90" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8927,49 +8927,49 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>565.6</v>
+        <v>591.7333333333333</v>
       </c>
       <c r="B92" t="n">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="C92" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D92" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E92" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F92" t="n">
+        <v>76</v>
+      </c>
+      <c r="G92" t="n">
+        <v>54</v>
+      </c>
+      <c r="H92" t="n">
         <v>74</v>
-      </c>
-      <c r="G92" t="n">
-        <v>52</v>
-      </c>
-      <c r="H92" t="n">
-        <v>70</v>
       </c>
       <c r="I92" t="n">
         <v>12</v>
       </c>
       <c r="J92" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K92" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="L92" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M92" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N92" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="O92" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="P92" t="n">
         <v>0</v>
@@ -9005,7 +9005,7 @@
         </is>
       </c>
       <c r="W92" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9020,52 +9020,52 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>359.9833333333333</v>
+        <v>377.8666666666667</v>
       </c>
       <c r="B93" t="n">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="C93" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D93" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E93" t="n">
         <v>2</v>
       </c>
       <c r="F93" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G93" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H93" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="I93" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J93" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K93" t="n">
         <v>15</v>
       </c>
       <c r="L93" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M93" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="N93" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="O93" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="P93" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         </is>
       </c>
       <c r="W93" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9206,16 +9206,16 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>298.3833333333333</v>
+        <v>310.5</v>
       </c>
       <c r="B95" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C95" t="n">
         <v>30</v>
       </c>
       <c r="D95" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E95" t="n">
         <v>7</v>
@@ -9224,16 +9224,16 @@
         <v>23</v>
       </c>
       <c r="G95" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H95" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I95" t="n">
         <v>21</v>
       </c>
       <c r="J95" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K95" t="n">
         <v>20</v>
@@ -9242,13 +9242,13 @@
         <v>5</v>
       </c>
       <c r="M95" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N95" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="O95" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P95" t="n">
         <v>3</v>
@@ -9284,7 +9284,7 @@
         </is>
       </c>
       <c r="W95" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9299,37 +9299,37 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>364.8666666666667</v>
+        <v>381.2</v>
       </c>
       <c r="B96" t="n">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="C96" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D96" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E96" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F96" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G96" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H96" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I96" t="n">
         <v>11</v>
       </c>
       <c r="J96" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K96" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L96" t="n">
         <v>11</v>
@@ -9338,10 +9338,10 @@
         <v>33</v>
       </c>
       <c r="N96" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O96" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="P96" t="n">
         <v>0</v>
@@ -9377,7 +9377,7 @@
         </is>
       </c>
       <c r="W96" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>387.8166666666667</v>
+        <v>398.1333333333333</v>
       </c>
       <c r="B98" t="n">
         <v>142</v>
@@ -9500,7 +9500,7 @@
         <v>23</v>
       </c>
       <c r="F98" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G98" t="n">
         <v>9</v>
@@ -9512,13 +9512,13 @@
         <v>14</v>
       </c>
       <c r="J98" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K98" t="n">
         <v>21</v>
       </c>
       <c r="L98" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M98" t="n">
         <v>23</v>
@@ -9563,7 +9563,7 @@
         </is>
       </c>
       <c r="W98" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9578,49 +9578,49 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>271.8166666666667</v>
+        <v>291.8833333333333</v>
       </c>
       <c r="B99" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="C99" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D99" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E99" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F99" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G99" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H99" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I99" t="n">
         <v>12</v>
       </c>
       <c r="J99" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K99" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L99" t="n">
         <v>7</v>
       </c>
       <c r="M99" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N99" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="O99" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="P99" t="n">
         <v>0</v>
@@ -9656,7 +9656,7 @@
         </is>
       </c>
       <c r="W99" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9671,37 +9671,37 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>646.5</v>
+        <v>678.9333333333333</v>
       </c>
       <c r="B100" t="n">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="C100" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D100" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E100" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F100" t="n">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="G100" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H100" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I100" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J100" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K100" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L100" t="n">
         <v>7</v>
@@ -9710,10 +9710,10 @@
         <v>22</v>
       </c>
       <c r="N100" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O100" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="P100" t="n">
         <v>1</v>
@@ -9749,7 +9749,7 @@
         </is>
       </c>
       <c r="W100" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9764,49 +9764,49 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>672.6</v>
+        <v>701.85</v>
       </c>
       <c r="B101" t="n">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="C101" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D101" t="n">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="E101" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F101" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G101" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H101" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I101" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J101" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="K101" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="L101" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M101" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="N101" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O101" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="P101" t="n">
         <v>2</v>
@@ -9842,7 +9842,7 @@
         </is>
       </c>
       <c r="W101" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>576.2833333333333</v>
+        <v>596.1</v>
       </c>
       <c r="B102" t="n">
         <v>210</v>
@@ -9866,13 +9866,13 @@
         <v>18</v>
       </c>
       <c r="D102" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E102" t="n">
         <v>50</v>
       </c>
       <c r="F102" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G102" t="n">
         <v>24</v>
@@ -9881,10 +9881,10 @@
         <v>41</v>
       </c>
       <c r="I102" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J102" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K102" t="n">
         <v>24</v>
@@ -9893,16 +9893,16 @@
         <v>9</v>
       </c>
       <c r="M102" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N102" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O102" t="n">
         <v>36</v>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         </is>
       </c>
       <c r="W102" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X102" t="inlineStr">
         <is>
@@ -9950,31 +9950,31 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>232.9833333333333</v>
+        <v>242.5833333333333</v>
       </c>
       <c r="B103" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C103" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D103" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E103" t="n">
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G103" t="n">
         <v>12</v>
       </c>
       <c r="H103" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I103" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J103" t="n">
         <v>37</v>
@@ -9989,10 +9989,10 @@
         <v>10</v>
       </c>
       <c r="N103" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="O103" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P103" t="n">
         <v>7</v>
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="W103" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X103" t="inlineStr">
         <is>
@@ -10043,10 +10043,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>2.45</v>
+        <v>20.11666666666667</v>
       </c>
       <c r="B104" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
@@ -10055,10 +10055,10 @@
         <v>0</v>
       </c>
       <c r="E104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F104" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -10067,22 +10067,22 @@
         <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K104" t="n">
         <v>0</v>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M104" t="n">
         <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -10121,7 +10121,7 @@
         </is>
       </c>
       <c r="W104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X104" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>65.95</v>
+        <v>75.81666666666666</v>
       </c>
       <c r="B107" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C107" t="n">
         <v>6</v>
@@ -10334,10 +10334,10 @@
         <v>8</v>
       </c>
       <c r="E107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F107" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G107" t="n">
         <v>4</v>
@@ -10349,10 +10349,10 @@
         <v>2</v>
       </c>
       <c r="J107" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L107" t="n">
         <v>1</v>
@@ -10400,7 +10400,7 @@
         </is>
       </c>
       <c r="W107" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X107" t="inlineStr">
         <is>
@@ -10694,49 +10694,49 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>285.6</v>
+        <v>306.5666666666667</v>
       </c>
       <c r="B111" t="n">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="C111" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D111" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E111" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F111" t="n">
+        <v>32</v>
+      </c>
+      <c r="G111" t="n">
+        <v>39</v>
+      </c>
+      <c r="H111" t="n">
+        <v>57</v>
+      </c>
+      <c r="I111" t="n">
+        <v>15</v>
+      </c>
+      <c r="J111" t="n">
         <v>28</v>
-      </c>
-      <c r="G111" t="n">
-        <v>36</v>
-      </c>
-      <c r="H111" t="n">
-        <v>50</v>
-      </c>
-      <c r="I111" t="n">
-        <v>13</v>
-      </c>
-      <c r="J111" t="n">
-        <v>26</v>
       </c>
       <c r="K111" t="n">
         <v>38</v>
       </c>
       <c r="L111" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M111" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="N111" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O111" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="P111" t="n">
         <v>1</v>
@@ -10772,7 +10772,7 @@
         </is>
       </c>
       <c r="W111" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X111" t="inlineStr">
         <is>
@@ -10787,16 +10787,16 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>652.0833333333334</v>
+        <v>683.95</v>
       </c>
       <c r="B112" t="n">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="C112" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="D112" t="n">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="E112" t="n">
         <v>3</v>
@@ -10805,34 +10805,34 @@
         <v>13</v>
       </c>
       <c r="G112" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H112" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="I112" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J112" t="n">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="K112" t="n">
         <v>22</v>
       </c>
       <c r="L112" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M112" t="n">
         <v>44</v>
       </c>
       <c r="N112" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="O112" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="P112" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -10865,7 +10865,7 @@
         </is>
       </c>
       <c r="W112" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X112" t="inlineStr">
         <is>
@@ -10880,49 +10880,49 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>627.5333333333333</v>
+        <v>648.9833333333333</v>
       </c>
       <c r="B113" t="n">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="C113" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D113" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E113" t="n">
         <v>26</v>
       </c>
       <c r="F113" t="n">
+        <v>66</v>
+      </c>
+      <c r="G113" t="n">
+        <v>45</v>
+      </c>
+      <c r="H113" t="n">
         <v>63</v>
       </c>
-      <c r="G113" t="n">
-        <v>44</v>
-      </c>
-      <c r="H113" t="n">
-        <v>62</v>
-      </c>
       <c r="I113" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J113" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K113" t="n">
         <v>47</v>
       </c>
       <c r="L113" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M113" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N113" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="O113" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P113" t="n">
         <v>4</v>
@@ -10958,7 +10958,7 @@
         </is>
       </c>
       <c r="W113" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X113" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>352.9166666666667</v>
+        <v>358.7333333333333</v>
       </c>
       <c r="B114" t="n">
         <v>89</v>
@@ -10988,7 +10988,7 @@
         <v>9</v>
       </c>
       <c r="F114" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G114" t="n">
         <v>24</v>
@@ -10997,13 +10997,13 @@
         <v>35</v>
       </c>
       <c r="I114" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J114" t="n">
         <v>47</v>
       </c>
       <c r="K114" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L114" t="n">
         <v>14</v>
@@ -11012,7 +11012,7 @@
         <v>17</v>
       </c>
       <c r="N114" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O114" t="n">
         <v>28</v>
@@ -11051,7 +11051,7 @@
         </is>
       </c>
       <c r="W114" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X114" t="inlineStr">
         <is>
@@ -11159,7 +11159,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>50.61666666666667</v>
+        <v>51.88333333333333</v>
       </c>
       <c r="B116" t="n">
         <v>22</v>
@@ -11237,7 +11237,7 @@
         </is>
       </c>
       <c r="W116" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X116" t="inlineStr">
         <is>
@@ -11252,49 +11252,49 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>544.85</v>
+        <v>562.4666666666667</v>
       </c>
       <c r="B117" t="n">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="C117" t="n">
         <v>50</v>
       </c>
       <c r="D117" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E117" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F117" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G117" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H117" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I117" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J117" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K117" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L117" t="n">
         <v>37</v>
       </c>
       <c r="M117" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N117" t="n">
         <v>29</v>
       </c>
       <c r="O117" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="P117" t="n">
         <v>2</v>
@@ -11330,7 +11330,7 @@
         </is>
       </c>
       <c r="W117" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X117" t="inlineStr">
         <is>
@@ -11345,52 +11345,52 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>680.6333333333333</v>
+        <v>716.9833333333333</v>
       </c>
       <c r="B118" t="n">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="C118" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D118" t="n">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="E118" t="n">
         <v>4</v>
       </c>
       <c r="F118" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G118" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H118" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I118" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="J118" t="n">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="K118" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="L118" t="n">
         <v>23</v>
       </c>
       <c r="M118" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N118" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="O118" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="P118" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         </is>
       </c>
       <c r="W118" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X118" t="inlineStr">
         <is>
@@ -11438,22 +11438,22 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>418.2333333333333</v>
+        <v>444.15</v>
       </c>
       <c r="B119" t="n">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="C119" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D119" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E119" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F119" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G119" t="n">
         <v>22</v>
@@ -11465,19 +11465,19 @@
         <v>4</v>
       </c>
       <c r="J119" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K119" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L119" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M119" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N119" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O119" t="n">
         <v>57</v>
@@ -11516,7 +11516,7 @@
         </is>
       </c>
       <c r="W119" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X119" t="inlineStr">
         <is>
@@ -11624,22 +11624,22 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>270.9833333333333</v>
+        <v>288.7166666666667</v>
       </c>
       <c r="B121" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C121" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D121" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E121" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F121" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G121" t="n">
         <v>14</v>
@@ -11654,19 +11654,19 @@
         <v>16</v>
       </c>
       <c r="K121" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L121" t="n">
         <v>3</v>
       </c>
       <c r="M121" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N121" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O121" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P121" t="n">
         <v>0</v>
@@ -11702,7 +11702,7 @@
         </is>
       </c>
       <c r="W121" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X121" t="inlineStr">
         <is>
@@ -11717,16 +11717,16 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>421.3166666666667</v>
+        <v>432.1333333333333</v>
       </c>
       <c r="B122" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C122" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D122" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E122" t="n">
         <v>4</v>
@@ -11741,7 +11741,7 @@
         <v>37</v>
       </c>
       <c r="I122" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J122" t="n">
         <v>62</v>
@@ -11750,13 +11750,13 @@
         <v>16</v>
       </c>
       <c r="L122" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M122" t="n">
         <v>29</v>
       </c>
       <c r="N122" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="O122" t="n">
         <v>26</v>
@@ -11795,7 +11795,7 @@
         </is>
       </c>
       <c r="W122" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X122" t="inlineStr">
         <is>
@@ -11810,22 +11810,22 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>269.2666666666667</v>
+        <v>291.0333333333334</v>
       </c>
       <c r="B123" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C123" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D123" t="n">
+        <v>38</v>
+      </c>
+      <c r="E123" t="n">
+        <v>14</v>
+      </c>
+      <c r="F123" t="n">
         <v>36</v>
-      </c>
-      <c r="E123" t="n">
-        <v>13</v>
-      </c>
-      <c r="F123" t="n">
-        <v>32</v>
       </c>
       <c r="G123" t="n">
         <v>12</v>
@@ -11834,25 +11834,25 @@
         <v>22</v>
       </c>
       <c r="I123" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J123" t="n">
         <v>30</v>
       </c>
       <c r="K123" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L123" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M123" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N123" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O123" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P123" t="n">
         <v>1</v>
@@ -11888,7 +11888,7 @@
         </is>
       </c>
       <c r="W123" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X123" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>559.3333333333334</v>
+        <v>563.3833333333333</v>
       </c>
       <c r="B128" t="n">
         <v>222</v>
@@ -12284,13 +12284,13 @@
         <v>58</v>
       </c>
       <c r="D128" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E128" t="n">
         <v>32</v>
       </c>
       <c r="F128" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G128" t="n">
         <v>10</v>
@@ -12299,7 +12299,7 @@
         <v>14</v>
       </c>
       <c r="I128" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J128" t="n">
         <v>27</v>
@@ -12353,7 +12353,7 @@
         </is>
       </c>
       <c r="W128" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X128" t="inlineStr">
         <is>
@@ -12368,49 +12368,49 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>701.2</v>
+        <v>736.0333333333333</v>
       </c>
       <c r="B129" t="n">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="C129" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D129" t="n">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="E129" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F129" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G129" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="H129" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="I129" t="n">
         <v>11</v>
       </c>
       <c r="J129" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="K129" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L129" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M129" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="N129" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="O129" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="P129" t="n">
         <v>3</v>
@@ -12446,7 +12446,7 @@
         </is>
       </c>
       <c r="W129" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X129" t="inlineStr">
         <is>
@@ -12461,52 +12461,52 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>307.5</v>
+        <v>333.15</v>
       </c>
       <c r="B130" t="n">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="C130" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D130" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="E130" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F130" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G130" t="n">
         <v>20</v>
       </c>
       <c r="H130" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I130" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J130" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K130" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L130" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M130" t="n">
         <v>33</v>
       </c>
       <c r="N130" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O130" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P130" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         </is>
       </c>
       <c r="W130" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X130" t="inlineStr">
         <is>
@@ -12554,10 +12554,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>93.98333333333333</v>
+        <v>99.25</v>
       </c>
       <c r="B131" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C131" t="n">
         <v>15</v>
@@ -12572,13 +12572,13 @@
         <v>1</v>
       </c>
       <c r="G131" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H131" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I131" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J131" t="n">
         <v>15</v>
@@ -12587,16 +12587,16 @@
         <v>3</v>
       </c>
       <c r="L131" t="n">
+        <v>8</v>
+      </c>
+      <c r="M131" t="n">
         <v>7</v>
       </c>
-      <c r="M131" t="n">
-        <v>4</v>
-      </c>
       <c r="N131" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O131" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P131" t="n">
         <v>1</v>
@@ -12632,7 +12632,7 @@
         </is>
       </c>
       <c r="W131" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X131" t="inlineStr">
         <is>
@@ -12740,40 +12740,40 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>379.3166666666667</v>
+        <v>400.7166666666666</v>
       </c>
       <c r="B133" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C133" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D133" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E133" t="n">
         <v>12</v>
       </c>
       <c r="F133" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G133" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H133" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I133" t="n">
         <v>14</v>
       </c>
       <c r="J133" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K133" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L133" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M133" t="n">
         <v>12</v>
@@ -12782,7 +12782,7 @@
         <v>23</v>
       </c>
       <c r="O133" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="P133" t="n">
         <v>3</v>
@@ -12818,7 +12818,7 @@
         </is>
       </c>
       <c r="W133" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X133" t="inlineStr">
         <is>
@@ -12833,49 +12833,49 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>419.9</v>
+        <v>438.65</v>
       </c>
       <c r="B134" t="n">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="C134" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D134" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E134" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F134" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G134" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H134" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I134" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J134" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K134" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="L134" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M134" t="n">
+        <v>43</v>
+      </c>
+      <c r="N134" t="n">
         <v>40</v>
       </c>
-      <c r="N134" t="n">
-        <v>37</v>
-      </c>
       <c r="O134" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P134" t="n">
         <v>2</v>
@@ -12911,7 +12911,7 @@
         </is>
       </c>
       <c r="W134" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X134" t="inlineStr">
         <is>
@@ -13019,49 +13019,49 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>533.6333333333333</v>
+        <v>558.7</v>
       </c>
       <c r="B136" t="n">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="C136" t="n">
         <v>27</v>
       </c>
       <c r="D136" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E136" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F136" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G136" t="n">
+        <v>51</v>
+      </c>
+      <c r="H136" t="n">
+        <v>64</v>
+      </c>
+      <c r="I136" t="n">
+        <v>5</v>
+      </c>
+      <c r="J136" t="n">
         <v>45</v>
       </c>
-      <c r="H136" t="n">
-        <v>58</v>
-      </c>
-      <c r="I136" t="n">
-        <v>3</v>
-      </c>
-      <c r="J136" t="n">
-        <v>44</v>
-      </c>
       <c r="K136" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="L136" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M136" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N136" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O136" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="P136" t="n">
         <v>0</v>
@@ -13097,7 +13097,7 @@
         </is>
       </c>
       <c r="W136" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X136" t="inlineStr">
         <is>
@@ -13112,16 +13112,16 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>382.9</v>
+        <v>395.35</v>
       </c>
       <c r="B137" t="n">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C137" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D137" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E137" t="n">
         <v>5</v>
@@ -13130,34 +13130,34 @@
         <v>32</v>
       </c>
       <c r="G137" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H137" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I137" t="n">
         <v>26</v>
       </c>
       <c r="J137" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K137" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L137" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M137" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N137" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O137" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P137" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         </is>
       </c>
       <c r="W137" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X137" t="inlineStr">
         <is>
@@ -13205,49 +13205,49 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>584.0333333333333</v>
+        <v>613.1333333333333</v>
       </c>
       <c r="B138" t="n">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="C138" t="n">
+        <v>89</v>
+      </c>
+      <c r="D138" t="n">
+        <v>157</v>
+      </c>
+      <c r="E138" t="n">
+        <v>15</v>
+      </c>
+      <c r="F138" t="n">
+        <v>59</v>
+      </c>
+      <c r="G138" t="n">
         <v>88</v>
       </c>
-      <c r="D138" t="n">
-        <v>154</v>
-      </c>
-      <c r="E138" t="n">
-        <v>13</v>
-      </c>
-      <c r="F138" t="n">
-        <v>53</v>
-      </c>
-      <c r="G138" t="n">
-        <v>84</v>
-      </c>
       <c r="H138" t="n">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="I138" t="n">
         <v>41</v>
       </c>
       <c r="J138" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="K138" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L138" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M138" t="n">
         <v>39</v>
       </c>
       <c r="N138" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O138" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="P138" t="n">
         <v>10</v>
@@ -13283,7 +13283,7 @@
         </is>
       </c>
       <c r="W138" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X138" t="inlineStr">
         <is>
@@ -13670,22 +13670,22 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>353.95</v>
+        <v>372.8</v>
       </c>
       <c r="B143" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C143" t="n">
         <v>16</v>
       </c>
       <c r="D143" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E143" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F143" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G143" t="n">
         <v>40</v>
@@ -13694,10 +13694,10 @@
         <v>59</v>
       </c>
       <c r="I143" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J143" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K143" t="n">
         <v>8</v>
@@ -13709,10 +13709,10 @@
         <v>22</v>
       </c>
       <c r="N143" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="O143" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P143" t="n">
         <v>1</v>
@@ -13748,7 +13748,7 @@
         </is>
       </c>
       <c r="W143" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X143" t="inlineStr">
         <is>
@@ -14135,34 +14135,34 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>383.5</v>
+        <v>409.3666666666667</v>
       </c>
       <c r="B148" t="n">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="C148" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D148" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="E148" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F148" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G148" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H148" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="I148" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J148" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="K148" t="n">
         <v>26</v>
@@ -14171,16 +14171,16 @@
         <v>8</v>
       </c>
       <c r="M148" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="N148" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="O148" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="P148" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         </is>
       </c>
       <c r="W148" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X148" t="inlineStr">
         <is>
@@ -14228,49 +14228,49 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>580.0833333333334</v>
+        <v>608.2</v>
       </c>
       <c r="B149" t="n">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="C149" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D149" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E149" t="n">
         <v>54</v>
       </c>
       <c r="F149" t="n">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="G149" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H149" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I149" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J149" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K149" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L149" t="n">
         <v>28</v>
       </c>
       <c r="M149" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N149" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O149" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="P149" t="n">
         <v>0</v>
@@ -14306,7 +14306,7 @@
         </is>
       </c>
       <c r="W149" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X149" t="inlineStr">
         <is>
@@ -14321,52 +14321,52 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>581.2333333333333</v>
+        <v>601.6333333333333</v>
       </c>
       <c r="B150" t="n">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="C150" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D150" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E150" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F150" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G150" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H150" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I150" t="n">
         <v>19</v>
       </c>
       <c r="J150" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K150" t="n">
         <v>26</v>
       </c>
       <c r="L150" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M150" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N150" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="O150" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P150" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         </is>
       </c>
       <c r="W150" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X150" t="inlineStr">
         <is>
@@ -14414,16 +14414,16 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>418.55</v>
+        <v>433.8166666666667</v>
       </c>
       <c r="B151" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C151" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D151" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E151" t="n">
         <v>6</v>
@@ -14432,16 +14432,16 @@
         <v>25</v>
       </c>
       <c r="G151" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H151" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I151" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J151" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K151" t="n">
         <v>20</v>
@@ -14450,16 +14450,16 @@
         <v>21</v>
       </c>
       <c r="M151" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="N151" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="O151" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P151" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         </is>
       </c>
       <c r="W151" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X151" t="inlineStr">
         <is>
@@ -14507,22 +14507,22 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>273.45</v>
+        <v>277.7166666666666</v>
       </c>
       <c r="B152" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C152" t="n">
         <v>11</v>
       </c>
       <c r="D152" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E152" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F152" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G152" t="n">
         <v>14</v>
@@ -14540,16 +14540,16 @@
         <v>17</v>
       </c>
       <c r="L152" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M152" t="n">
         <v>10</v>
       </c>
       <c r="N152" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O152" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P152" t="n">
         <v>1</v>
@@ -14585,7 +14585,7 @@
         </is>
       </c>
       <c r="W152" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X152" t="inlineStr">
         <is>
@@ -14600,22 +14600,22 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>496.6333333333333</v>
+        <v>517.7666666666667</v>
       </c>
       <c r="B153" t="n">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="C153" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D153" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E153" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F153" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G153" t="n">
         <v>54</v>
@@ -14627,25 +14627,25 @@
         <v>12</v>
       </c>
       <c r="J153" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K153" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="L153" t="n">
         <v>20</v>
       </c>
       <c r="M153" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N153" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="O153" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P153" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         </is>
       </c>
       <c r="W153" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X153" t="inlineStr">
         <is>
@@ -14693,10 +14693,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>391.1</v>
+        <v>411.65</v>
       </c>
       <c r="B154" t="n">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C154" t="n">
         <v>24</v>
@@ -14708,34 +14708,34 @@
         <v>18</v>
       </c>
       <c r="F154" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G154" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H154" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="I154" t="n">
         <v>10</v>
       </c>
       <c r="J154" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K154" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L154" t="n">
         <v>16</v>
       </c>
       <c r="M154" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N154" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="O154" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="P154" t="n">
         <v>2</v>
@@ -14771,7 +14771,7 @@
         </is>
       </c>
       <c r="W154" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X154" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>474.6</v>
+        <v>493.0666666666667</v>
       </c>
       <c r="B155" t="n">
         <v>160</v>
@@ -14795,40 +14795,40 @@
         <v>45</v>
       </c>
       <c r="D155" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E155" t="n">
         <v>16</v>
       </c>
       <c r="F155" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G155" t="n">
         <v>22</v>
       </c>
       <c r="H155" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I155" t="n">
         <v>32</v>
       </c>
       <c r="J155" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K155" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L155" t="n">
         <v>29</v>
       </c>
       <c r="M155" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N155" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O155" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P155" t="n">
         <v>2</v>
@@ -14864,7 +14864,7 @@
         </is>
       </c>
       <c r="W155" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X155" t="inlineStr">
         <is>
@@ -14972,49 +14972,49 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>622.9166666666666</v>
+        <v>648.45</v>
       </c>
       <c r="B157" t="n">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="C157" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D157" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E157" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F157" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G157" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H157" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I157" t="n">
         <v>16</v>
       </c>
       <c r="J157" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="K157" t="n">
         <v>19</v>
       </c>
       <c r="L157" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M157" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N157" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O157" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="P157" t="n">
         <v>0</v>
@@ -15050,7 +15050,7 @@
         </is>
       </c>
       <c r="W157" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X157" t="inlineStr">
         <is>
@@ -15065,22 +15065,22 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>528.65</v>
+        <v>551.2</v>
       </c>
       <c r="B158" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C158" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D158" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E158" t="n">
         <v>57</v>
       </c>
       <c r="F158" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="G158" t="n">
         <v>54</v>
@@ -15092,25 +15092,25 @@
         <v>7</v>
       </c>
       <c r="J158" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K158" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L158" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M158" t="n">
         <v>31</v>
       </c>
       <c r="N158" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="O158" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         </is>
       </c>
       <c r="W158" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X158" t="inlineStr">
         <is>
@@ -15158,16 +15158,16 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>401.45</v>
+        <v>426.8333333333333</v>
       </c>
       <c r="B159" t="n">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="C159" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D159" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E159" t="n">
         <v>0</v>
@@ -15179,28 +15179,28 @@
         <v>26</v>
       </c>
       <c r="H159" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I159" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J159" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K159" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L159" t="n">
         <v>8</v>
       </c>
       <c r="M159" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N159" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="O159" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="P159" t="n">
         <v>4</v>
@@ -15236,7 +15236,7 @@
         </is>
       </c>
       <c r="W159" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X159" t="inlineStr">
         <is>
@@ -15344,49 +15344,49 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>388.4833333333333</v>
+        <v>409.0666666666667</v>
       </c>
       <c r="B161" t="n">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="C161" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D161" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E161" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F161" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G161" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H161" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="I161" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J161" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K161" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L161" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="M161" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N161" t="n">
         <v>45</v>
       </c>
       <c r="O161" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="P161" t="n">
         <v>2</v>
@@ -15422,7 +15422,7 @@
         </is>
       </c>
       <c r="W161" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X161" t="inlineStr">
         <is>
@@ -15437,16 +15437,16 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>361.3666666666667</v>
+        <v>375.5166666666667</v>
       </c>
       <c r="B162" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C162" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D162" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E162" t="n">
         <v>0</v>
@@ -15455,16 +15455,16 @@
         <v>3</v>
       </c>
       <c r="G162" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H162" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I162" t="n">
         <v>24</v>
       </c>
       <c r="J162" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K162" t="n">
         <v>3</v>
@@ -15473,16 +15473,16 @@
         <v>6</v>
       </c>
       <c r="M162" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N162" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="O162" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="P162" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         </is>
       </c>
       <c r="W162" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X162" t="inlineStr">
         <is>
@@ -15530,22 +15530,22 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>57.88333333333333</v>
+        <v>70</v>
       </c>
       <c r="B163" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C163" t="n">
         <v>4</v>
       </c>
       <c r="D163" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E163" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F163" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G163" t="n">
         <v>5</v>
@@ -15557,7 +15557,7 @@
         <v>1</v>
       </c>
       <c r="J163" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K163" t="n">
         <v>2</v>
@@ -15569,7 +15569,7 @@
         <v>5</v>
       </c>
       <c r="N163" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O163" t="n">
         <v>5</v>
@@ -15608,7 +15608,7 @@
         </is>
       </c>
       <c r="W163" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X163" t="inlineStr">
         <is>
@@ -15623,49 +15623,49 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>323.7</v>
+        <v>351.3333333333333</v>
       </c>
       <c r="B164" t="n">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="C164" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D164" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E164" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F164" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G164" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H164" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I164" t="n">
         <v>7</v>
       </c>
       <c r="J164" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K164" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L164" t="n">
         <v>18</v>
       </c>
       <c r="M164" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N164" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O164" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="P164" t="n">
         <v>0</v>
@@ -15701,7 +15701,7 @@
         </is>
       </c>
       <c r="W164" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X164" t="inlineStr">
         <is>
@@ -15809,37 +15809,37 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>270.4166666666667</v>
+        <v>295.2333333333333</v>
       </c>
       <c r="B166" t="n">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C166" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D166" t="n">
+        <v>61</v>
+      </c>
+      <c r="E166" t="n">
+        <v>14</v>
+      </c>
+      <c r="F166" t="n">
+        <v>40</v>
+      </c>
+      <c r="G166" t="n">
+        <v>40</v>
+      </c>
+      <c r="H166" t="n">
         <v>59</v>
       </c>
-      <c r="E166" t="n">
-        <v>13</v>
-      </c>
-      <c r="F166" t="n">
-        <v>39</v>
-      </c>
-      <c r="G166" t="n">
-        <v>36</v>
-      </c>
-      <c r="H166" t="n">
-        <v>50</v>
-      </c>
       <c r="I166" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J166" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K166" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L166" t="n">
         <v>12</v>
@@ -15848,10 +15848,10 @@
         <v>6</v>
       </c>
       <c r="N166" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O166" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="P166" t="n">
         <v>3</v>
@@ -15887,7 +15887,7 @@
         </is>
       </c>
       <c r="W166" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X166" t="inlineStr">
         <is>
@@ -15902,22 +15902,22 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>483.7</v>
+        <v>501.1</v>
       </c>
       <c r="B167" t="n">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="C167" t="n">
         <v>35</v>
       </c>
       <c r="D167" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E167" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F167" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G167" t="n">
         <v>48</v>
@@ -15929,13 +15929,13 @@
         <v>15</v>
       </c>
       <c r="J167" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K167" t="n">
         <v>18</v>
       </c>
       <c r="L167" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M167" t="n">
         <v>20</v>
@@ -15944,7 +15944,7 @@
         <v>54</v>
       </c>
       <c r="O167" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P167" t="n">
         <v>5</v>
@@ -15980,7 +15980,7 @@
         </is>
       </c>
       <c r="W167" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X167" t="inlineStr">
         <is>
@@ -16088,16 +16088,16 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>355.3333333333333</v>
+        <v>372.7</v>
       </c>
       <c r="B169" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C169" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D169" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E169" t="n">
         <v>1</v>
@@ -16112,10 +16112,10 @@
         <v>33</v>
       </c>
       <c r="I169" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J169" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="K169" t="n">
         <v>8</v>
@@ -16127,7 +16127,7 @@
         <v>14</v>
       </c>
       <c r="N169" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="O169" t="n">
         <v>32</v>
@@ -16166,7 +16166,7 @@
         </is>
       </c>
       <c r="W169" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X169" t="inlineStr">
         <is>
@@ -16181,7 +16181,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>394.5166666666667</v>
+        <v>399.8666666666667</v>
       </c>
       <c r="B170" t="n">
         <v>119</v>
@@ -16190,7 +16190,7 @@
         <v>35</v>
       </c>
       <c r="D170" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E170" t="n">
         <v>13</v>
@@ -16205,22 +16205,22 @@
         <v>17</v>
       </c>
       <c r="I170" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J170" t="n">
         <v>45</v>
       </c>
       <c r="K170" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L170" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M170" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N170" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O170" t="n">
         <v>20</v>
@@ -16259,7 +16259,7 @@
         </is>
       </c>
       <c r="W170" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X170" t="inlineStr">
         <is>
@@ -16460,16 +16460,16 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>399.6666666666667</v>
+        <v>412.3333333333333</v>
       </c>
       <c r="B173" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C173" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D173" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E173" t="n">
         <v>0</v>
@@ -16484,13 +16484,13 @@
         <v>45</v>
       </c>
       <c r="I173" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J173" t="n">
         <v>68</v>
       </c>
       <c r="K173" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L173" t="n">
         <v>7</v>
@@ -16499,13 +16499,13 @@
         <v>26</v>
       </c>
       <c r="N173" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O173" t="n">
         <v>40</v>
       </c>
       <c r="P173" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q173" t="inlineStr">
         <is>
@@ -16538,7 +16538,7 @@
         </is>
       </c>
       <c r="W173" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X173" t="inlineStr">
         <is>
@@ -16553,34 +16553,34 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>16.13333333333333</v>
+        <v>39.46666666666667</v>
       </c>
       <c r="B174" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="C174" t="n">
+        <v>3</v>
+      </c>
+      <c r="D174" t="n">
+        <v>6</v>
+      </c>
+      <c r="E174" t="n">
+        <v>5</v>
+      </c>
+      <c r="F174" t="n">
+        <v>14</v>
+      </c>
+      <c r="G174" t="n">
+        <v>4</v>
+      </c>
+      <c r="H174" t="n">
+        <v>4</v>
+      </c>
+      <c r="I174" t="n">
         <v>1</v>
       </c>
-      <c r="D174" t="n">
-        <v>3</v>
-      </c>
-      <c r="E174" t="n">
-        <v>2</v>
-      </c>
-      <c r="F174" t="n">
+      <c r="J174" t="n">
         <v>4</v>
-      </c>
-      <c r="G174" t="n">
-        <v>0</v>
-      </c>
-      <c r="H174" t="n">
-        <v>0</v>
-      </c>
-      <c r="I174" t="n">
-        <v>0</v>
-      </c>
-      <c r="J174" t="n">
-        <v>2</v>
       </c>
       <c r="K174" t="n">
         <v>6</v>
@@ -16589,49 +16589,49 @@
         <v>0</v>
       </c>
       <c r="M174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N174" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O174" t="n">
+        <v>5</v>
+      </c>
+      <c r="P174" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>https://imagenes.feb.es/Foto.aspx?c=2734740</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>MOODY, AANEN JOEL</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>https://baloncestoenvivo.feb.es/Jugador.aspx?i=981309&amp;c=2734740</t>
+        </is>
+      </c>
+      <c r="W174" t="n">
         <v>2</v>
-      </c>
-      <c r="P174" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q174" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R174" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="S174" t="inlineStr">
-        <is>
-          <t>https://imagenes.feb.es/Foto.aspx?c=2734740</t>
-        </is>
-      </c>
-      <c r="T174" t="inlineStr">
-        <is>
-          <t>MOODY, AANEN JOEL</t>
-        </is>
-      </c>
-      <c r="U174" t="inlineStr">
-        <is>
-          <t>INSOLAC CAJA 87</t>
-        </is>
-      </c>
-      <c r="V174" t="inlineStr">
-        <is>
-          <t>https://baloncestoenvivo.feb.es/Jugador.aspx?i=981309&amp;c=2734740</t>
-        </is>
-      </c>
-      <c r="W174" t="n">
-        <v>1</v>
       </c>
       <c r="X174" t="inlineStr">
         <is>
@@ -16646,49 +16646,49 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>481.1</v>
+        <v>501.0833333333333</v>
       </c>
       <c r="B175" t="n">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="C175" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D175" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="E175" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F175" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G175" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H175" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I175" t="n">
         <v>13</v>
       </c>
       <c r="J175" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K175" t="n">
         <v>71</v>
       </c>
       <c r="L175" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M175" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N175" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O175" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="P175" t="n">
         <v>1</v>
@@ -16724,7 +16724,7 @@
         </is>
       </c>
       <c r="W175" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X175" t="inlineStr">
         <is>
@@ -16925,16 +16925,16 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>483.5333333333333</v>
+        <v>507.3833333333333</v>
       </c>
       <c r="B178" t="n">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="C178" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D178" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="E178" t="n">
         <v>2</v>
@@ -16943,31 +16943,31 @@
         <v>15</v>
       </c>
       <c r="G178" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H178" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I178" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J178" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="K178" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L178" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M178" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N178" t="n">
         <v>55</v>
       </c>
       <c r="O178" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="P178" t="n">
         <v>3</v>
@@ -17003,7 +17003,7 @@
         </is>
       </c>
       <c r="W178" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X178" t="inlineStr">
         <is>
@@ -17018,22 +17018,22 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>551.5833333333334</v>
+        <v>570.8333333333334</v>
       </c>
       <c r="B179" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C179" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D179" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E179" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F179" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G179" t="n">
         <v>37</v>
@@ -17051,10 +17051,10 @@
         <v>19</v>
       </c>
       <c r="L179" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M179" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N179" t="n">
         <v>35</v>
@@ -17096,7 +17096,7 @@
         </is>
       </c>
       <c r="W179" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X179" t="inlineStr">
         <is>
@@ -17297,7 +17297,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>242.6666666666667</v>
+        <v>251.0166666666667</v>
       </c>
       <c r="B182" t="n">
         <v>122</v>
@@ -17312,7 +17312,7 @@
         <v>13</v>
       </c>
       <c r="F182" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G182" t="n">
         <v>23</v>
@@ -17327,19 +17327,19 @@
         <v>24</v>
       </c>
       <c r="K182" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L182" t="n">
         <v>6</v>
       </c>
       <c r="M182" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N182" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O182" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P182" t="n">
         <v>0</v>
@@ -17375,7 +17375,7 @@
         </is>
       </c>
       <c r="W182" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X182" t="inlineStr">
         <is>
@@ -17390,85 +17390,85 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>56.6</v>
+        <v>75.8</v>
       </c>
       <c r="B183" t="n">
+        <v>27</v>
+      </c>
+      <c r="C183" t="n">
+        <v>7</v>
+      </c>
+      <c r="D183" t="n">
+        <v>20</v>
+      </c>
+      <c r="E183" t="n">
+        <v>1</v>
+      </c>
+      <c r="F183" t="n">
+        <v>12</v>
+      </c>
+      <c r="G183" t="n">
+        <v>10</v>
+      </c>
+      <c r="H183" t="n">
         <v>16</v>
-      </c>
-      <c r="C183" t="n">
-        <v>4</v>
-      </c>
-      <c r="D183" t="n">
-        <v>14</v>
-      </c>
-      <c r="E183" t="n">
-        <v>0</v>
-      </c>
-      <c r="F183" t="n">
-        <v>10</v>
-      </c>
-      <c r="G183" t="n">
-        <v>8</v>
-      </c>
-      <c r="H183" t="n">
-        <v>12</v>
       </c>
       <c r="I183" t="n">
         <v>5</v>
       </c>
       <c r="J183" t="n">
+        <v>3</v>
+      </c>
+      <c r="K183" t="n">
+        <v>6</v>
+      </c>
+      <c r="L183" t="n">
         <v>2</v>
       </c>
-      <c r="K183" t="n">
-        <v>3</v>
-      </c>
-      <c r="L183" t="n">
-        <v>1</v>
-      </c>
       <c r="M183" t="n">
+        <v>8</v>
+      </c>
+      <c r="N183" t="n">
+        <v>11</v>
+      </c>
+      <c r="O183" t="n">
+        <v>13</v>
+      </c>
+      <c r="P183" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>https://imagenes.feb.es/Foto.aspx?c=1587901</t>
+        </is>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>VERGARA HARBOE, GUILLERMO</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>https://baloncestoenvivo.feb.es/Jugador.aspx?i=981320&amp;c=1587901</t>
+        </is>
+      </c>
+      <c r="W183" t="n">
         <v>5</v>
-      </c>
-      <c r="N183" t="n">
-        <v>9</v>
-      </c>
-      <c r="O183" t="n">
-        <v>9</v>
-      </c>
-      <c r="P183" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q183" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R183" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="S183" t="inlineStr">
-        <is>
-          <t>https://imagenes.feb.es/Foto.aspx?c=1587901</t>
-        </is>
-      </c>
-      <c r="T183" t="inlineStr">
-        <is>
-          <t>VERGARA HARBOE, GUILLERMO</t>
-        </is>
-      </c>
-      <c r="U183" t="inlineStr">
-        <is>
-          <t>JAEN PARAÍSO INTERIOR CB</t>
-        </is>
-      </c>
-      <c r="V183" t="inlineStr">
-        <is>
-          <t>https://baloncestoenvivo.feb.es/Jugador.aspx?i=981320&amp;c=1587901</t>
-        </is>
-      </c>
-      <c r="W183" t="n">
-        <v>4</v>
       </c>
       <c r="X183" t="inlineStr">
         <is>
@@ -17576,49 +17576,49 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>514.7833333333333</v>
+        <v>533.0833333333334</v>
       </c>
       <c r="B185" t="n">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C185" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D185" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E185" t="n">
+        <v>20</v>
+      </c>
+      <c r="F185" t="n">
+        <v>81</v>
+      </c>
+      <c r="G185" t="n">
+        <v>31</v>
+      </c>
+      <c r="H185" t="n">
+        <v>46</v>
+      </c>
+      <c r="I185" t="n">
+        <v>38</v>
+      </c>
+      <c r="J185" t="n">
+        <v>77</v>
+      </c>
+      <c r="K185" t="n">
         <v>19</v>
       </c>
-      <c r="F185" t="n">
-        <v>79</v>
-      </c>
-      <c r="G185" t="n">
-        <v>30</v>
-      </c>
-      <c r="H185" t="n">
-        <v>44</v>
-      </c>
-      <c r="I185" t="n">
-        <v>33</v>
-      </c>
-      <c r="J185" t="n">
-        <v>74</v>
-      </c>
-      <c r="K185" t="n">
-        <v>16</v>
-      </c>
       <c r="L185" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M185" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N185" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="O185" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="P185" t="n">
         <v>2</v>
@@ -17654,7 +17654,7 @@
         </is>
       </c>
       <c r="W185" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X185" t="inlineStr">
         <is>
@@ -17762,16 +17762,16 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>448.7166666666667</v>
+        <v>473.95</v>
       </c>
       <c r="B187" t="n">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="C187" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D187" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E187" t="n">
         <v>0</v>
@@ -17786,28 +17786,28 @@
         <v>73</v>
       </c>
       <c r="I187" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J187" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K187" t="n">
         <v>21</v>
       </c>
       <c r="L187" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M187" t="n">
         <v>31</v>
       </c>
       <c r="N187" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="O187" t="n">
         <v>47</v>
       </c>
       <c r="P187" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         </is>
       </c>
       <c r="W187" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X187" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>469.4</v>
+        <v>477.15</v>
       </c>
       <c r="B189" t="n">
         <v>100</v>
@@ -17957,7 +17957,7 @@
         <v>12</v>
       </c>
       <c r="D189" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E189" t="n">
         <v>17</v>
@@ -17978,16 +17978,16 @@
         <v>51</v>
       </c>
       <c r="K189" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L189" t="n">
         <v>19</v>
       </c>
       <c r="M189" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N189" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O189" t="n">
         <v>34</v>
@@ -18026,7 +18026,7 @@
         </is>
       </c>
       <c r="W189" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X189" t="inlineStr">
         <is>
@@ -18041,16 +18041,16 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>152.7166666666667</v>
+        <v>157.2166666666667</v>
       </c>
       <c r="B190" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C190" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D190" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E190" t="n">
         <v>0</v>
@@ -18119,7 +18119,7 @@
         </is>
       </c>
       <c r="W190" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X190" t="inlineStr">
         <is>
@@ -18320,10 +18320,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>438.75</v>
+        <v>451.1833333333333</v>
       </c>
       <c r="B193" t="n">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="C193" t="n">
         <v>37</v>
@@ -18332,22 +18332,22 @@
         <v>81</v>
       </c>
       <c r="E193" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F193" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G193" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H193" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I193" t="n">
         <v>37</v>
       </c>
       <c r="J193" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K193" t="n">
         <v>20</v>
@@ -18359,10 +18359,10 @@
         <v>34</v>
       </c>
       <c r="N193" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="O193" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P193" t="n">
         <v>4</v>
@@ -18398,7 +18398,7 @@
         </is>
       </c>
       <c r="W193" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X193" t="inlineStr">
         <is>
@@ -18413,22 +18413,22 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>547.2666666666667</v>
+        <v>573.8833333333333</v>
       </c>
       <c r="B194" t="n">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="C194" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D194" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="E194" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F194" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G194" t="n">
         <v>58</v>
@@ -18440,19 +18440,19 @@
         <v>24</v>
       </c>
       <c r="J194" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K194" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L194" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M194" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N194" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O194" t="n">
         <v>66</v>
@@ -18491,7 +18491,7 @@
         </is>
       </c>
       <c r="W194" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X194" t="inlineStr">
         <is>
@@ -18506,49 +18506,49 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>280.45</v>
+        <v>313.6833333333333</v>
       </c>
       <c r="B195" t="n">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="C195" t="n">
+        <v>17</v>
+      </c>
+      <c r="D195" t="n">
+        <v>39</v>
+      </c>
+      <c r="E195" t="n">
+        <v>37</v>
+      </c>
+      <c r="F195" t="n">
+        <v>103</v>
+      </c>
+      <c r="G195" t="n">
+        <v>10</v>
+      </c>
+      <c r="H195" t="n">
+        <v>21</v>
+      </c>
+      <c r="I195" t="n">
+        <v>7</v>
+      </c>
+      <c r="J195" t="n">
+        <v>27</v>
+      </c>
+      <c r="K195" t="n">
+        <v>20</v>
+      </c>
+      <c r="L195" t="n">
         <v>14</v>
-      </c>
-      <c r="D195" t="n">
-        <v>33</v>
-      </c>
-      <c r="E195" t="n">
-        <v>34</v>
-      </c>
-      <c r="F195" t="n">
-        <v>92</v>
-      </c>
-      <c r="G195" t="n">
-        <v>9</v>
-      </c>
-      <c r="H195" t="n">
-        <v>19</v>
-      </c>
-      <c r="I195" t="n">
-        <v>5</v>
-      </c>
-      <c r="J195" t="n">
-        <v>23</v>
-      </c>
-      <c r="K195" t="n">
-        <v>15</v>
-      </c>
-      <c r="L195" t="n">
-        <v>13</v>
       </c>
       <c r="M195" t="n">
         <v>15</v>
       </c>
       <c r="N195" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="O195" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="P195" t="n">
         <v>0</v>
@@ -18584,7 +18584,7 @@
         </is>
       </c>
       <c r="W195" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X195" t="inlineStr">
         <is>
@@ -18599,16 +18599,16 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>268.9666666666666</v>
+        <v>279.2333333333333</v>
       </c>
       <c r="B196" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C196" t="n">
         <v>33</v>
       </c>
       <c r="D196" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E196" t="n">
         <v>1</v>
@@ -18617,13 +18617,13 @@
         <v>16</v>
       </c>
       <c r="G196" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H196" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I196" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J196" t="n">
         <v>38</v>
@@ -18638,13 +18638,13 @@
         <v>34</v>
       </c>
       <c r="N196" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O196" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="P196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         </is>
       </c>
       <c r="W196" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X196" t="inlineStr">
         <is>
@@ -18692,49 +18692,49 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>446.3666666666667</v>
+        <v>476.6666666666667</v>
       </c>
       <c r="B197" t="n">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="C197" t="n">
         <v>50</v>
       </c>
       <c r="D197" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E197" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F197" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="G197" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H197" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="I197" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J197" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="K197" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L197" t="n">
         <v>18</v>
       </c>
       <c r="M197" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N197" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="O197" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="P197" t="n">
         <v>1</v>
@@ -18770,7 +18770,7 @@
         </is>
       </c>
       <c r="W197" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X197" t="inlineStr">
         <is>
@@ -18785,22 +18785,22 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>228.0666666666667</v>
+        <v>240.2333333333333</v>
       </c>
       <c r="B198" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C198" t="n">
         <v>11</v>
       </c>
       <c r="D198" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E198" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F198" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G198" t="n">
         <v>9</v>
@@ -18815,16 +18815,16 @@
         <v>12</v>
       </c>
       <c r="K198" t="n">
+        <v>6</v>
+      </c>
+      <c r="L198" t="n">
         <v>5</v>
       </c>
-      <c r="L198" t="n">
-        <v>4</v>
-      </c>
       <c r="M198" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N198" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="O198" t="n">
         <v>16</v>
@@ -18863,7 +18863,7 @@
         </is>
       </c>
       <c r="W198" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X198" t="inlineStr">
         <is>
@@ -18878,49 +18878,49 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>534.1833333333333</v>
+        <v>551.9333333333333</v>
       </c>
       <c r="B199" t="n">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="C199" t="n">
         <v>55</v>
       </c>
       <c r="D199" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E199" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F199" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G199" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H199" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="I199" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J199" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K199" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L199" t="n">
         <v>36</v>
       </c>
       <c r="M199" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N199" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O199" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="P199" t="n">
         <v>2</v>
@@ -18956,7 +18956,7 @@
         </is>
       </c>
       <c r="W199" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X199" t="inlineStr">
         <is>
@@ -18971,16 +18971,16 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>403.7166666666667</v>
+        <v>426.3833333333333</v>
       </c>
       <c r="B200" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C200" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D200" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E200" t="n">
         <v>12</v>
@@ -18995,25 +18995,25 @@
         <v>19</v>
       </c>
       <c r="I200" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J200" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K200" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="L200" t="n">
         <v>10</v>
       </c>
       <c r="M200" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N200" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O200" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P200" t="n">
         <v>0</v>
@@ -19049,7 +19049,7 @@
         </is>
       </c>
       <c r="W200" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X200" t="inlineStr">
         <is>
@@ -19064,22 +19064,22 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>681.2833333333333</v>
+        <v>710.3166666666667</v>
       </c>
       <c r="B201" t="n">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="C201" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D201" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E201" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F201" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="G201" t="n">
         <v>62</v>
@@ -19088,19 +19088,19 @@
         <v>82</v>
       </c>
       <c r="I201" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J201" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K201" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L201" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M201" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N201" t="n">
         <v>52</v>
@@ -19142,7 +19142,7 @@
         </is>
       </c>
       <c r="W201" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X201" t="inlineStr">
         <is>
@@ -19157,10 +19157,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>60.65000000000001</v>
+        <v>66.43333333333334</v>
       </c>
       <c r="B202" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C202" t="n">
         <v>4</v>
@@ -19169,10 +19169,10 @@
         <v>8</v>
       </c>
       <c r="E202" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F202" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G202" t="n">
         <v>4</v>
@@ -19187,7 +19187,7 @@
         <v>0</v>
       </c>
       <c r="K202" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L202" t="n">
         <v>1</v>
@@ -19196,7 +19196,7 @@
         <v>1</v>
       </c>
       <c r="N202" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O202" t="n">
         <v>9</v>
@@ -19235,7 +19235,7 @@
         </is>
       </c>
       <c r="W202" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X202" t="inlineStr">
         <is>
@@ -19250,16 +19250,16 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>475.6833333333333</v>
+        <v>497.5833333333333</v>
       </c>
       <c r="B203" t="n">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="C203" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D203" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E203" t="n">
         <v>0</v>
@@ -19268,31 +19268,31 @@
         <v>0</v>
       </c>
       <c r="G203" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H203" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="I203" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J203" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K203" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L203" t="n">
         <v>6</v>
       </c>
       <c r="M203" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="N203" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O203" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="P203" t="n">
         <v>6</v>
@@ -19328,7 +19328,7 @@
         </is>
       </c>
       <c r="W203" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X203" t="inlineStr">
         <is>
@@ -19343,49 +19343,49 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>368.3833333333333</v>
+        <v>382.4166666666667</v>
       </c>
       <c r="B204" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C204" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D204" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E204" t="n">
         <v>8</v>
       </c>
       <c r="F204" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G204" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H204" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="I204" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J204" t="n">
+        <v>34</v>
+      </c>
+      <c r="K204" t="n">
         <v>32</v>
       </c>
-      <c r="K204" t="n">
-        <v>29</v>
-      </c>
       <c r="L204" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M204" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N204" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O204" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="P204" t="n">
         <v>1</v>
@@ -19421,7 +19421,7 @@
         </is>
       </c>
       <c r="W204" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X204" t="inlineStr">
         <is>
@@ -19436,16 +19436,16 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>586</v>
+        <v>602.9166666666666</v>
       </c>
       <c r="B205" t="n">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C205" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D205" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E205" t="n">
         <v>24</v>
@@ -19454,34 +19454,34 @@
         <v>86</v>
       </c>
       <c r="G205" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H205" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I205" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J205" t="n">
         <v>66</v>
       </c>
       <c r="K205" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L205" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M205" t="n">
         <v>25</v>
       </c>
       <c r="N205" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O205" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="P205" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q205" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         </is>
       </c>
       <c r="W205" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X205" t="inlineStr">
         <is>
@@ -19529,28 +19529,28 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>391.25</v>
+        <v>419.5166666666667</v>
       </c>
       <c r="B206" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C206" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D206" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E206" t="n">
         <v>10</v>
       </c>
       <c r="F206" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G206" t="n">
         <v>19</v>
       </c>
       <c r="H206" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I206" t="n">
         <v>20</v>
@@ -19559,7 +19559,7 @@
         <v>43</v>
       </c>
       <c r="K206" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L206" t="n">
         <v>12</v>
@@ -19568,10 +19568,10 @@
         <v>15</v>
       </c>
       <c r="N206" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="O206" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="P206" t="n">
         <v>5</v>
@@ -19607,7 +19607,7 @@
         </is>
       </c>
       <c r="W206" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X206" t="inlineStr">
         <is>
@@ -19808,22 +19808,22 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>360.6666666666667</v>
+        <v>374.05</v>
       </c>
       <c r="B209" t="n">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C209" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D209" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E209" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F209" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G209" t="n">
         <v>24</v>
@@ -19835,19 +19835,19 @@
         <v>13</v>
       </c>
       <c r="J209" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K209" t="n">
         <v>17</v>
       </c>
       <c r="L209" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M209" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="N209" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O209" t="n">
         <v>37</v>
@@ -19886,7 +19886,7 @@
         </is>
       </c>
       <c r="W209" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X209" t="inlineStr">
         <is>
@@ -19901,16 +19901,16 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>391.0166666666667</v>
+        <v>409.6833333333333</v>
       </c>
       <c r="B210" t="n">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="C210" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D210" t="n">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="E210" t="n">
         <v>0</v>
@@ -19919,16 +19919,16 @@
         <v>3</v>
       </c>
       <c r="G210" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H210" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I210" t="n">
         <v>58</v>
       </c>
       <c r="J210" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="K210" t="n">
         <v>9</v>
@@ -19940,10 +19940,10 @@
         <v>34</v>
       </c>
       <c r="N210" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O210" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P210" t="n">
         <v>2</v>
@@ -19979,7 +19979,7 @@
         </is>
       </c>
       <c r="W210" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X210" t="inlineStr">
         <is>
@@ -19994,28 +19994,28 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>67.28333333333333</v>
+        <v>78.88333333333333</v>
       </c>
       <c r="B211" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D211" t="n">
+        <v>4</v>
+      </c>
+      <c r="E211" t="n">
         <v>2</v>
       </c>
-      <c r="E211" t="n">
-        <v>1</v>
-      </c>
       <c r="F211" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G211" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H211" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I211" t="n">
         <v>4</v>
@@ -20033,10 +20033,10 @@
         <v>2</v>
       </c>
       <c r="N211" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O211" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P211" t="n">
         <v>0</v>
@@ -20072,7 +20072,7 @@
         </is>
       </c>
       <c r="W211" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X211" t="inlineStr">
         <is>
@@ -20087,22 +20087,22 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>483.3833333333333</v>
+        <v>503.3666666666667</v>
       </c>
       <c r="B212" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C212" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D212" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E212" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F212" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G212" t="n">
         <v>17</v>
@@ -20117,19 +20117,19 @@
         <v>32</v>
       </c>
       <c r="K212" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L212" t="n">
         <v>14</v>
       </c>
       <c r="M212" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N212" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="O212" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P212" t="n">
         <v>1</v>
@@ -20165,7 +20165,7 @@
         </is>
       </c>
       <c r="W212" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X212" t="inlineStr">
         <is>
@@ -20180,52 +20180,52 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>488.0833333333333</v>
+        <v>515.4833333333333</v>
       </c>
       <c r="B213" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C213" t="n">
         <v>16</v>
       </c>
       <c r="D213" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E213" t="n">
         <v>14</v>
       </c>
       <c r="F213" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G213" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H213" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I213" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J213" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="K213" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L213" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M213" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N213" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="O213" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="P213" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q213" t="inlineStr">
         <is>
@@ -20258,7 +20258,7 @@
         </is>
       </c>
       <c r="W213" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X213" t="inlineStr">
         <is>
@@ -20273,49 +20273,49 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>476.5166666666667</v>
+        <v>499.3833333333333</v>
       </c>
       <c r="B214" t="n">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="C214" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D214" t="n">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="E214" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F214" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="G214" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H214" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="I214" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J214" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K214" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L214" t="n">
         <v>17</v>
       </c>
       <c r="M214" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N214" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="O214" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="P214" t="n">
         <v>0</v>
@@ -20351,7 +20351,7 @@
         </is>
       </c>
       <c r="W214" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X214" t="inlineStr">
         <is>
@@ -20552,49 +20552,49 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>603.8</v>
+        <v>640.7833333333333</v>
       </c>
       <c r="B217" t="n">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="C217" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D217" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="E217" t="n">
         <v>12</v>
       </c>
       <c r="F217" t="n">
+        <v>51</v>
+      </c>
+      <c r="G217" t="n">
+        <v>53</v>
+      </c>
+      <c r="H217" t="n">
+        <v>71</v>
+      </c>
+      <c r="I217" t="n">
+        <v>55</v>
+      </c>
+      <c r="J217" t="n">
+        <v>81</v>
+      </c>
+      <c r="K217" t="n">
+        <v>31</v>
+      </c>
+      <c r="L217" t="n">
+        <v>22</v>
+      </c>
+      <c r="M217" t="n">
+        <v>29</v>
+      </c>
+      <c r="N217" t="n">
         <v>47</v>
       </c>
-      <c r="G217" t="n">
-        <v>51</v>
-      </c>
-      <c r="H217" t="n">
+      <c r="O217" t="n">
         <v>68</v>
-      </c>
-      <c r="I217" t="n">
-        <v>53</v>
-      </c>
-      <c r="J217" t="n">
-        <v>79</v>
-      </c>
-      <c r="K217" t="n">
-        <v>30</v>
-      </c>
-      <c r="L217" t="n">
-        <v>20</v>
-      </c>
-      <c r="M217" t="n">
-        <v>27</v>
-      </c>
-      <c r="N217" t="n">
-        <v>44</v>
-      </c>
-      <c r="O217" t="n">
-        <v>64</v>
       </c>
       <c r="P217" t="n">
         <v>12</v>
@@ -20630,7 +20630,7 @@
         </is>
       </c>
       <c r="W217" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X217" t="inlineStr">
         <is>
@@ -20645,16 +20645,16 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>335.95</v>
+        <v>353.2</v>
       </c>
       <c r="B218" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C218" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D218" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E218" t="n">
         <v>0</v>
@@ -20669,10 +20669,10 @@
         <v>42</v>
       </c>
       <c r="I218" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J218" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="K218" t="n">
         <v>9</v>
@@ -20681,16 +20681,16 @@
         <v>12</v>
       </c>
       <c r="M218" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N218" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="O218" t="n">
         <v>39</v>
       </c>
       <c r="P218" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q218" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         </is>
       </c>
       <c r="W218" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X218" t="inlineStr">
         <is>
@@ -20738,34 +20738,34 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>415.6</v>
+        <v>446.3333333333333</v>
       </c>
       <c r="B219" t="n">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="C219" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D219" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="E219" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F219" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="G219" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H219" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I219" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J219" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K219" t="n">
         <v>38</v>
@@ -20774,16 +20774,16 @@
         <v>17</v>
       </c>
       <c r="M219" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="N219" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O219" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="P219" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q219" t="inlineStr">
         <is>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="W219" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X219" t="inlineStr">
         <is>
@@ -20831,85 +20831,85 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>71.7</v>
+        <v>94.81666666666666</v>
       </c>
       <c r="B220" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="C220" t="n">
+        <v>11</v>
+      </c>
+      <c r="D220" t="n">
+        <v>25</v>
+      </c>
+      <c r="E220" t="n">
+        <v>6</v>
+      </c>
+      <c r="F220" t="n">
+        <v>17</v>
+      </c>
+      <c r="G220" t="n">
+        <v>11</v>
+      </c>
+      <c r="H220" t="n">
+        <v>15</v>
+      </c>
+      <c r="I220" t="n">
         <v>8</v>
-      </c>
-      <c r="D220" t="n">
-        <v>21</v>
-      </c>
-      <c r="E220" t="n">
-        <v>4</v>
-      </c>
-      <c r="F220" t="n">
-        <v>12</v>
-      </c>
-      <c r="G220" t="n">
-        <v>10</v>
-      </c>
-      <c r="H220" t="n">
-        <v>13</v>
-      </c>
-      <c r="I220" t="n">
-        <v>5</v>
       </c>
       <c r="J220" t="n">
         <v>8</v>
       </c>
       <c r="K220" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L220" t="n">
         <v>0</v>
       </c>
       <c r="M220" t="n">
+        <v>6</v>
+      </c>
+      <c r="N220" t="n">
+        <v>9</v>
+      </c>
+      <c r="O220" t="n">
+        <v>11</v>
+      </c>
+      <c r="P220" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>https://imagenes.feb.es/Foto.aspx?c=2536645</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>UKAWUBA, ROBERT CHIMA</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>https://baloncestoenvivo.feb.es/Jugador.aspx?i=981342&amp;c=2536645</t>
+        </is>
+      </c>
+      <c r="W220" t="n">
         <v>5</v>
-      </c>
-      <c r="N220" t="n">
-        <v>7</v>
-      </c>
-      <c r="O220" t="n">
-        <v>10</v>
-      </c>
-      <c r="P220" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q220" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="R220" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="S220" t="inlineStr">
-        <is>
-          <t>https://imagenes.feb.es/Foto.aspx?c=2536645</t>
-        </is>
-      </c>
-      <c r="T220" t="inlineStr">
-        <is>
-          <t>UKAWUBA, ROBERT CHIMA</t>
-        </is>
-      </c>
-      <c r="U220" t="inlineStr">
-        <is>
-          <t>REINA PROTEÍNAS CLAVIJO</t>
-        </is>
-      </c>
-      <c r="V220" t="inlineStr">
-        <is>
-          <t>https://baloncestoenvivo.feb.es/Jugador.aspx?i=981342&amp;c=2536645</t>
-        </is>
-      </c>
-      <c r="W220" t="n">
-        <v>4</v>
       </c>
       <c r="X220" t="inlineStr">
         <is>
@@ -21203,49 +21203,49 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>440.8833333333333</v>
+        <v>462.55</v>
       </c>
       <c r="B224" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C224" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D224" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E224" t="n">
         <v>2</v>
       </c>
       <c r="F224" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G224" t="n">
         <v>30</v>
       </c>
       <c r="H224" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I224" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J224" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="K224" t="n">
         <v>11</v>
       </c>
       <c r="L224" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M224" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N224" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O224" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P224" t="n">
         <v>18</v>
@@ -21281,7 +21281,7 @@
         </is>
       </c>
       <c r="W224" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X224" t="inlineStr">
         <is>
